--- a/Data/Building/MeetingRoomTwo.UltravioletLevel.xlsx
+++ b/Data/Building/MeetingRoomTwo.UltravioletLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H449"/>
+  <dimension ref="A1:I421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260952</v>
+        <v>1711852997</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260980</v>
+        <v>1711853015</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709261014</v>
+        <v>1711853050</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709261063</v>
+        <v>1711853087</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709261124</v>
+        <v>1711853116</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709264994</v>
+        <v>1711853156</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709268914</v>
+        <v>1711859532</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709272826</v>
+        <v>1711859569</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +737,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709272853</v>
+        <v>1711861212</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +774,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709272881</v>
+        <v>1711867532</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +807,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709274125</v>
+        <v>1711869154</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709274153</v>
+        <v>1711869623</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +873,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709274190</v>
+        <v>1711910601</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709274211</v>
+        <v>1711924275</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +939,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709274301</v>
+        <v>1711930063</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +976,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709275508</v>
+        <v>1711931584</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1009,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709277245</v>
+        <v>1711931620</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1042,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709277749</v>
+        <v>1711931638</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1075,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709243145</v>
+        <v>1711932081</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1108,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709250303</v>
+        <v>1711932108</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1141,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1160,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709253391</v>
+        <v>1711932122</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1170,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709253425</v>
+        <v>1711932161</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1203,15 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709254687</v>
+        <v>1711932212</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1240,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709254724</v>
+        <v>1711935322</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1273,15 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1300,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709256006</v>
+        <v>1711938805</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1314,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1333,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709263371</v>
+        <v>1711942034</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1347,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709265351</v>
+        <v>1711942064</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1380,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709265372</v>
+        <v>1711942094</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1413,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709266076</v>
+        <v>1711943659</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1446,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709266102</v>
+        <v>1711943700</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1479,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709266136</v>
+        <v>1711943748</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1512,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709266208</v>
+        <v>1711943784</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1541,15 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709266630</v>
+        <v>1711943841</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1578,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709266660</v>
+        <v>1711944432</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1611,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709267645</v>
+        <v>1711945669</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1648,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709268388</v>
+        <v>1711945999</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1681,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709318832</v>
+        <v>1712008165</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1714,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709332050</v>
+        <v>1712016610</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709338432</v>
+        <v>1712022265</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1780,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709339428</v>
+        <v>1712029821</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1813,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1832,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709339462</v>
+        <v>1712032916</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1846,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1865,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709339487</v>
+        <v>1712032937</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1879,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1898,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709340678</v>
+        <v>1712033786</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1912,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1931,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709340727</v>
+        <v>1712033812</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1945,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1964,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709340765</v>
+        <v>1712034592</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1974,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1997,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709340790</v>
+        <v>1712035391</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2007,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2030,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709340873</v>
+        <v>1712084006</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2040,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2063,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709345785</v>
+        <v>1712097811</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2073,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2096,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709349665</v>
+        <v>1712104257</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2110,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2129,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709353181</v>
+        <v>1712105501</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2143,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2162,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709353227</v>
+        <v>1712105531</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2176,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2195,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709353260</v>
+        <v>1712105555</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2209,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2228,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709354329</v>
+        <v>1712106052</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2242,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2261,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709354370</v>
+        <v>1712106076</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2275,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2294,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709354391</v>
+        <v>1712106102</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2308,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2327,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709354422</v>
+        <v>1712106129</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2364,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709354492</v>
+        <v>1712106192</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2378,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2397,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709355976</v>
+        <v>1712112044</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2407,15 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2434,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709357159</v>
+        <v>1712116520</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2444,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2467,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709357760</v>
+        <v>1712119404</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2477,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2500,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709403537</v>
+        <v>1712119431</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2514,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2533,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709417326</v>
+        <v>1712119462</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2543,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2566,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709423499</v>
+        <v>1712120376</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2576,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2599,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709425903</v>
+        <v>1712120427</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2613,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2632,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709425938</v>
+        <v>1712120461</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2642,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2665,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709425963</v>
+        <v>1712120485</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2675,15 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2702,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709427263</v>
+        <v>1712120526</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2712,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2735,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709427290</v>
+        <v>1712120562</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2749,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2768,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709427317</v>
+        <v>1712120591</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2778,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2801,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709427342</v>
+        <v>1712120615</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2811,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2834,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709427399</v>
+        <v>1712121765</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2844,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2867,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709430224</v>
+        <v>1712121787</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2877,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2900,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709433842</v>
+        <v>1712121805</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2914,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2933,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709438597</v>
+        <v>1712121833</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2943,15 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2970,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709438635</v>
+        <v>1712121903</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2980,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3003,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709438674</v>
+        <v>1712123493</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3013,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3036,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709441685</v>
+        <v>1712124634</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3050,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709441725</v>
+        <v>1712125297</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3079,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3102,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709441757</v>
+        <v>1712169321</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3112,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3135,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709441803</v>
+        <v>1712181751</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3149,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3168,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709442153</v>
+        <v>1712187913</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3178,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3201,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709442645</v>
+        <v>1712194915</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3211,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3238,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709499572</v>
+        <v>1712199218</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3248,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3271,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709508226</v>
+        <v>1712206324</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3285,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3304,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709513391</v>
+        <v>1712208305</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3318,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3337,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709513430</v>
+        <v>1712208840</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3351,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3370,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709514449</v>
+        <v>1712264506</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3384,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3403,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709514486</v>
+        <v>1712271885</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3417,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3436,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709514511</v>
+        <v>1712276063</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3446,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3469,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709514536</v>
+        <v>1712276091</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3479,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3502,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709514624</v>
+        <v>1712278968</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3512,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3535,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709521775</v>
+        <v>1712278990</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3549,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3568,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709524241</v>
+        <v>1712279020</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3578,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3601,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709524271</v>
+        <v>1712279053</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3611,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3638,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709577541</v>
+        <v>1712279118</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3648,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3671,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709591373</v>
+        <v>1712285619</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3685,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3704,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709597813</v>
+        <v>1712290850</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3714,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3737,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709599431</v>
+        <v>1712290894</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3747,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3770,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709599474</v>
+        <v>1712343463</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3784,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3803,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709599498</v>
+        <v>1712356758</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3813,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3836,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709600899</v>
+        <v>1712363774</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3846,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3869,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709600917</v>
+        <v>1712371717</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3879,15 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3906,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709600946</v>
+        <v>1712377848</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3920,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3939,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709600966</v>
+        <v>1712386782</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3949,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3972,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709601035</v>
+        <v>1712389273</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +3982,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4005,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709605416</v>
+        <v>1712390227</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4015,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4038,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709608843</v>
+        <v>1712430410</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4048,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4071,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709614315</v>
+        <v>1712444211</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4085,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4104,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709614343</v>
+        <v>1712451934</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3953,10 +4114,11 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4137,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709614373</v>
+        <v>1712460704</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4147,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4174,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709615449</v>
+        <v>1712465055</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4184,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4207,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709615478</v>
+        <v>1712474073</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4221,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4240,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709615508</v>
+        <v>1712476606</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4250,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4273,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709615539</v>
+        <v>1712477331</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4283,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4306,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709615619</v>
+        <v>1712516881</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4316,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4339,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709615732</v>
+        <v>1712530163</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4353,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4372,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709616815</v>
+        <v>1712535905</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4382,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4405,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709617445</v>
+        <v>1712538198</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4415,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4438,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709664404</v>
+        <v>1712538220</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4452,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4471,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709678143</v>
+        <v>1712538243</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4481,11 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4504,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709685132</v>
+        <v>1712540020</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4514,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4537,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709693583</v>
+        <v>1712540050</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4547,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4570,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1709698727</v>
+        <v>1712540081</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4584,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4603,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1709698757</v>
+        <v>1712540101</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4613,15 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4640,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1709698798</v>
+        <v>1712540172</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4654,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4673,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1709707358</v>
+        <v>1712543151</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4683,15 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4710,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1709709421</v>
+        <v>1712546849</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4720,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4743,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1709710115</v>
+        <v>1712548402</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4753,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4776,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1709761321</v>
+        <v>1712548426</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4790,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4809,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1709770668</v>
+        <v>1712548453</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4819,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4842,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1709777429</v>
+        <v>1712549184</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4852,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4875,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1709785998</v>
+        <v>1712549222</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4889,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4908,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1709792047</v>
+        <v>1712549263</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4918,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4941,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1709793274</v>
+        <v>1712549298</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4951,15 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4978,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1709836728</v>
+        <v>1712549379</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +4988,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5011,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1709849431</v>
+        <v>1712550717</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5025,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5044,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1709854671</v>
+        <v>1712550746</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5054,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5077,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1709855718</v>
+        <v>1712550777</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5087,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5110,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1709855752</v>
+        <v>1712551411</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5124,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5143,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1709855779</v>
+        <v>1712551438</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5153,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5176,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1709857026</v>
+        <v>1712551464</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5186,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5209,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1709857051</v>
+        <v>1712551493</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5219,15 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5246,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1709857081</v>
+        <v>1712551567</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5260,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5279,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1709857111</v>
+        <v>1712552410</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5289,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5312,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1709857171</v>
+        <v>1712553425</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5322,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5345,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1709860933</v>
+        <v>1712553986</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5355,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5378,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1709864550</v>
+        <v>1712601263</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5388,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5411,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1709870298</v>
+        <v>1712615479</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5425,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5444,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1709871315</v>
+        <v>1712621591</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5454,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5477,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1709871915</v>
+        <v>1712624653</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5487,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5510,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1709923237</v>
+        <v>1712624683</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5524,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5543,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1709936523</v>
+        <v>1712624706</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5553,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5576,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1709941913</v>
+        <v>1712625832</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5586,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5609,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1709944910</v>
+        <v>1712625859</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5623,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5642,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1709944961</v>
+        <v>1712625887</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5652,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5675,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1709944994</v>
+        <v>1712625925</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5685,15 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5712,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1709945132</v>
+        <v>1712625997</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5722,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5745,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1709945174</v>
+        <v>1712628298</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5755,15 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5782,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1709945200</v>
+        <v>1712631849</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5796,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5815,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1709945235</v>
+        <v>1712636737</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5825,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5848,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1709945330</v>
+        <v>1712636766</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5858,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5881,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1709948372</v>
+        <v>1712636788</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5891,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5914,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1709951882</v>
+        <v>1712637564</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5924,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5947,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1709958074</v>
+        <v>1712637587</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5961,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5980,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1709959853</v>
+        <v>1712638637</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5994,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6013,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1709960203</v>
+        <v>1712638680</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6027,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6046,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710010075</v>
+        <v>1712638726</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6060,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6079,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710024237</v>
+        <v>1712639160</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6089,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6112,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710030688</v>
+        <v>1712701804</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6122,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6145,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710032565</v>
+        <v>1712709785</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6159,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6178,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710032603</v>
+        <v>1712712375</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6192,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6211,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710032635</v>
+        <v>1712712399</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6225,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6244,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710032795</v>
+        <v>1712714151</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6258,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6277,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710032847</v>
+        <v>1712714167</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6291,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6310,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710032903</v>
+        <v>1712715005</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6324,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6343,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710032926</v>
+        <v>1712722148</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6097,10 +6353,11 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6376,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710033007</v>
+        <v>1712722719</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6386,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6409,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710037486</v>
+        <v>1712722761</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6419,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6442,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710041750</v>
+        <v>1712723970</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6452,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6475,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710047107</v>
+        <v>1712723989</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6489,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6508,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710047127</v>
+        <v>1712724017</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6518,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6541,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710047158</v>
+        <v>1712724099</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6289,10 +6551,11 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6574,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710048966</v>
+        <v>1712726623</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6588,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6607,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710048990</v>
+        <v>1712727484</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6617,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6640,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710050129</v>
+        <v>1712775885</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6654,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6673,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710050688</v>
+        <v>1712790567</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6683,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6706,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710097087</v>
+        <v>1712797137</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6716,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6739,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710111063</v>
+        <v>1712798495</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6753,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6772,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710117523</v>
+        <v>1712798518</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +6782,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6805,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710117963</v>
+        <v>1712798551</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6815,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6838,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710117995</v>
+        <v>1712799897</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6852,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6871,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710118025</v>
+        <v>1712799930</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6881,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6904,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710126293</v>
+        <v>1712799945</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6914,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6937,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710126336</v>
+        <v>1712799976</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +6947,15 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6974,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710126374</v>
+        <v>1712800069</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +6988,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7007,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710126401</v>
+        <v>1712803099</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +7021,11 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7044,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710128730</v>
+        <v>1712806265</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7058,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7077,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710132477</v>
+        <v>1712811134</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7091,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7110,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710132525</v>
+        <v>1712812596</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7124,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7143,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710132555</v>
+        <v>1712812976</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7157,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7176,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710133847</v>
+        <v>1712860971</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7190,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7209,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710133886</v>
+        <v>1712875212</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7223,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7242,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710133901</v>
+        <v>1712881711</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7256,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7275,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710133927</v>
+        <v>1712888407</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7289,11 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7312,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710134007</v>
+        <v>1712891239</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7326,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7345,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710135138</v>
+        <v>1712896208</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7359,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7378,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710136660</v>
+        <v>1712896231</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7392,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7411,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710136690</v>
+        <v>1712896256</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7425,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7444,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710136737</v>
+        <v>1712897782</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7458,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7477,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710137317</v>
+        <v>1712897819</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7487,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7510,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710181571</v>
+        <v>1712897850</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7217,10 +7520,11 @@
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7543,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710195516</v>
+        <v>1712897909</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7557,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7576,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710202262</v>
+        <v>1712898472</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7586,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7609,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710204370</v>
+        <v>1712899292</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7619,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7642,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710204394</v>
+        <v>1712946191</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7656,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7675,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710204427</v>
+        <v>1712959735</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7685,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7708,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710205961</v>
+        <v>1712967545</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7409,10 +7718,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7741,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710205988</v>
+        <v>1712976335</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7441,10 +7751,15 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7778,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710206020</v>
+        <v>1712980601</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7477,6 +7792,7 @@
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7811,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710206043</v>
+        <v>1712988424</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +7821,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7844,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710206093</v>
+        <v>1712990340</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7537,10 +7854,11 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7877,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710208705</v>
+        <v>1712991198</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7887,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7910,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710213723</v>
+        <v>1713034522</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7601,10 +7920,11 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7943,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710219146</v>
+        <v>1713047793</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7957,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7976,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710219170</v>
+        <v>1713055555</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +7986,11 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8009,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710219199</v>
+        <v>1713064286</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7697,10 +8019,15 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8046,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710219482</v>
+        <v>1713069588</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7729,10 +8056,11 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8079,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710219507</v>
+        <v>1713077960</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7765,6 +8093,7 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8112,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710219535</v>
+        <v>1713079490</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7793,10 +8122,11 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8145,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710219560</v>
+        <v>1713080139</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7825,10 +8155,11 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8178,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710219649</v>
+        <v>1713129805</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8188,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8211,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710220526</v>
+        <v>1713137351</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7893,6 +8225,7 @@
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8244,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710222609</v>
+        <v>1713140730</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8258,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8277,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710223304</v>
+        <v>1713140755</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7957,6 +8291,7 @@
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8310,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1710268346</v>
+        <v>1713141564</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7989,6 +8324,7 @@
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8343,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1710281651</v>
+        <v>1713141608</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8357,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8376,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1710289163</v>
+        <v>1713141660</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8053,6 +8390,7 @@
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8409,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1710297558</v>
+        <v>1713141717</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8419,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8442,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1710302138</v>
+        <v>1713142415</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8456,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8475,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1710311200</v>
+        <v>1713149731</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8149,6 +8489,7 @@
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8508,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1710313944</v>
+        <v>1713152314</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8522,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8541,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1710314879</v>
+        <v>1713152334</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8213,6 +8555,7 @@
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8574,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1710365524</v>
+        <v>1713153722</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8245,6 +8588,7 @@
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8607,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1710375796</v>
+        <v>1713153746</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8621,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8640,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1710383335</v>
+        <v>1713153778</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8654,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8673,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1710392938</v>
+        <v>1713153836</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8687,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8706,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1710399752</v>
+        <v>1713154606</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8720,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8739,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1710401069</v>
+        <v>1713155446</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8753,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8772,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1710441816</v>
+        <v>1713206547</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8437,6 +8786,7 @@
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8805,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1710455734</v>
+        <v>1713219275</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8469,6 +8819,7 @@
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8838,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1710461668</v>
+        <v>1713224837</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8852,7 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8871,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1710463435</v>
+        <v>1713226292</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8533,6 +8885,7 @@
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8904,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1710463466</v>
+        <v>1713226330</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8565,6 +8918,7 @@
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8937,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1710463508</v>
+        <v>1713226351</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8951,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +8970,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1710464680</v>
+        <v>1713227353</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8629,6 +8984,7 @@
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +9003,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1710464704</v>
+        <v>1713227392</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8657,10 +9013,11 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +9036,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1710464728</v>
+        <v>1713227877</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8689,10 +9046,11 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +9069,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1710464753</v>
+        <v>1713227896</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8721,10 +9079,11 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9102,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1710464817</v>
+        <v>1713227919</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8757,6 +9116,7 @@
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9135,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1710467900</v>
+        <v>1713227951</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8789,6 +9149,11 @@
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9172,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1710471029</v>
+        <v>1713227995</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8821,6 +9186,7 @@
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9205,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1710477014</v>
+        <v>1713231117</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8849,10 +9215,15 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9242,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1710478868</v>
+        <v>1713235334</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8881,10 +9252,11 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9275,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1710479566</v>
+        <v>1713238222</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8913,10 +9285,11 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8935,7 +9308,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1710527341</v>
+        <v>1713238247</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8949,6 +9322,7 @@
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8967,7 +9341,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1710540774</v>
+        <v>1713238312</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8977,10 +9351,11 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8999,7 +9374,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1710546232</v>
+        <v>1713238851</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -9009,10 +9384,11 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,7 +9407,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1710548867</v>
+        <v>1713238882</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9045,6 +9421,7 @@
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9063,7 +9440,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1710548900</v>
+        <v>1713238912</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9073,10 +9450,11 @@
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9095,7 +9473,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1710548933</v>
+        <v>1713238935</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9105,10 +9483,15 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9127,7 +9510,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1710549388</v>
+        <v>1713238998</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9137,10 +9520,11 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9159,7 +9543,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1710549427</v>
+        <v>1713240786</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9173,6 +9557,7 @@
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9191,7 +9576,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1710549456</v>
+        <v>1713241589</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9201,10 +9586,11 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9223,7 +9609,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1710549487</v>
+        <v>1713242043</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9233,10 +9619,11 @@
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9255,7 +9642,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1710549582</v>
+        <v>1713293638</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9265,10 +9652,11 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9287,7 +9675,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1710552958</v>
+        <v>1713306626</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9297,10 +9685,11 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9319,7 +9708,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1710557136</v>
+        <v>1713312149</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9333,6 +9722,7 @@
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9351,7 +9741,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1710562980</v>
+        <v>1713314513</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -9365,6 +9755,7 @@
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9383,7 +9774,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1710563006</v>
+        <v>1713314555</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9397,6 +9788,7 @@
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9415,7 +9807,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1710563017</v>
+        <v>1713314581</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9429,6 +9821,7 @@
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9447,7 +9840,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1710564835</v>
+        <v>1713315242</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9461,6 +9854,7 @@
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9479,7 +9873,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1710565120</v>
+        <v>1713315269</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -9489,10 +9883,11 @@
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9511,7 +9906,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1710615297</v>
+        <v>1713315303</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -9521,10 +9916,11 @@
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9543,7 +9939,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1710629443</v>
+        <v>1713315330</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9553,10 +9949,15 @@
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9575,7 +9976,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1710635654</v>
+        <v>1713315414</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9589,6 +9990,7 @@
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9607,7 +10009,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1710642699</v>
+        <v>1713318670</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9621,6 +10023,11 @@
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9639,7 +10046,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1710646115</v>
+        <v>1713321848</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9653,6 +10060,7 @@
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9671,7 +10079,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1710650480</v>
+        <v>1713325124</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9685,6 +10093,7 @@
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9703,7 +10112,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1710650514</v>
+        <v>1713325152</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9717,6 +10126,7 @@
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9735,7 +10145,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1710650554</v>
+        <v>1713325177</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9749,6 +10159,7 @@
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9767,7 +10178,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1710653999</v>
+        <v>1713326960</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9781,6 +10192,7 @@
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9799,7 +10211,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1710654082</v>
+        <v>1713327027</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9809,10 +10221,11 @@
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9831,7 +10244,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1710700280</v>
+        <v>1713327087</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9841,10 +10254,11 @@
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9863,7 +10277,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1710714355</v>
+        <v>1713327184</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9877,6 +10291,7 @@
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9895,7 +10310,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1710720298</v>
+        <v>1713327530</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9905,10 +10320,11 @@
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9927,7 +10343,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1710722325</v>
+        <v>1713327957</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9937,10 +10353,11 @@
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9959,7 +10376,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1710722350</v>
+        <v>1713388600</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9973,6 +10390,7 @@
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9991,7 +10409,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1710722394</v>
+        <v>1713395578</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10001,10 +10419,11 @@
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10023,7 +10442,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1710723832</v>
+        <v>1713400358</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -10033,10 +10452,11 @@
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10055,7 +10475,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1710723866</v>
+        <v>1713406706</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -10069,6 +10489,7 @@
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10087,7 +10508,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1710723907</v>
+        <v>1713409337</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -10097,10 +10518,11 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10119,7 +10541,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1710723934</v>
+        <v>1713409372</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -10129,10 +10551,11 @@
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10151,7 +10574,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1710723980</v>
+        <v>1713487972</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -10161,10 +10584,11 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10183,7 +10607,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1710726952</v>
+        <v>1713488000</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -10193,10 +10617,11 @@
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10215,7 +10640,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1710730101</v>
+        <v>1713488027</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -10229,6 +10654,7 @@
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10247,7 +10673,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1710734922</v>
+        <v>1713488059</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -10257,10 +10683,15 @@
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10279,7 +10710,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1710734959</v>
+        <v>1713488132</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -10289,10 +10720,11 @@
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10311,7 +10743,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1710734994</v>
+        <v>1713491581</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -10321,10 +10753,15 @@
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10343,7 +10780,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1710736444</v>
+        <v>1713494871</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -10353,10 +10790,11 @@
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10375,7 +10813,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1710736488</v>
+        <v>1713498560</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -10389,6 +10827,7 @@
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10407,7 +10846,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1710736520</v>
+        <v>1713498578</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -10417,10 +10856,11 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10439,7 +10879,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1710736604</v>
+        <v>1713498607</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -10449,10 +10889,11 @@
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10471,7 +10912,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1710737157</v>
+        <v>1713499929</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -10485,6 +10926,7 @@
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10503,7 +10945,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1710737739</v>
+        <v>1713499996</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -10513,10 +10955,11 @@
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10535,7 +10978,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1710787347</v>
+        <v>1713500011</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -10545,10 +10988,11 @@
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10567,7 +11011,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1710801352</v>
+        <v>1713500089</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -10581,6 +11025,7 @@
         </is>
       </c>
       <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10599,7 +11044,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1710807530</v>
+        <v>1713500966</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -10609,10 +11054,11 @@
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10631,7 +11077,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1710808665</v>
+        <v>1713501338</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -10641,10 +11087,11 @@
       <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10663,7 +11110,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1710808704</v>
+        <v>1713552556</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10677,6 +11124,7 @@
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10695,7 +11143,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1710808746</v>
+        <v>1713565891</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10705,10 +11153,11 @@
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10727,7 +11176,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1710810967</v>
+        <v>1713572660</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10737,10 +11186,11 @@
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10759,7 +11209,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1710810998</v>
+        <v>1713579957</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10769,10 +11219,15 @@
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10791,7 +11246,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1710811028</v>
+        <v>1713584155</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10805,6 +11260,7 @@
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10823,7 +11279,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1710811059</v>
+        <v>1713591051</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10833,10 +11289,11 @@
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10855,7 +11312,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1710811129</v>
+        <v>1713592765</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10865,10 +11322,11 @@
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10887,7 +11345,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1710814130</v>
+        <v>1713593568</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10897,10 +11355,11 @@
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10919,7 +11378,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1710818051</v>
+        <v>1713637138</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10929,10 +11388,11 @@
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10951,7 +11411,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1710822421</v>
+        <v>1713650979</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10965,6 +11425,7 @@
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10983,7 +11444,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1710822461</v>
+        <v>1713658670</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10993,10 +11454,11 @@
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11015,7 +11477,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1710822493</v>
+        <v>1713667210</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -11025,10 +11487,15 @@
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11047,7 +11514,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1710822713</v>
+        <v>1713671470</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -11057,10 +11524,11 @@
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11079,7 +11547,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1710822760</v>
+        <v>1713679526</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -11093,6 +11561,7 @@
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11111,7 +11580,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1710822788</v>
+        <v>1713681675</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -11121,10 +11590,11 @@
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11143,7 +11613,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1710822814</v>
+        <v>1713682341</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -11153,10 +11623,11 @@
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11175,7 +11646,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1710822910</v>
+        <v>1713725402</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -11185,10 +11656,11 @@
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11207,7 +11679,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1710824567</v>
+        <v>1713738285</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -11221,6 +11693,7 @@
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11239,7 +11712,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1710826128</v>
+        <v>1713744184</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -11249,10 +11722,11 @@
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11271,7 +11745,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1710826710</v>
+        <v>1713744891</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -11281,10 +11755,11 @@
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11303,7 +11778,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1710873904</v>
+        <v>1713744921</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -11317,6 +11792,7 @@
         </is>
       </c>
       <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11335,7 +11811,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1710887289</v>
+        <v>1713744959</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -11345,10 +11821,11 @@
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11367,7 +11844,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1710894969</v>
+        <v>1713745922</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -11377,10 +11854,11 @@
       <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11399,7 +11877,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1710903889</v>
+        <v>1713745946</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -11409,10 +11887,11 @@
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11431,7 +11910,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1710909429</v>
+        <v>1713745973</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -11445,6 +11924,7 @@
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11463,7 +11943,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1710918122</v>
+        <v>1713746011</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -11473,10 +11953,15 @@
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11495,7 +11980,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1710920011</v>
+        <v>1713746096</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -11505,10 +11990,11 @@
       <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11527,7 +12013,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1710920927</v>
+        <v>1713750192</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -11537,10 +12023,15 @@
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11559,7 +12050,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1710960954</v>
+        <v>1713753772</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -11569,10 +12060,11 @@
       <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11591,7 +12083,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1710974810</v>
+        <v>1713755522</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -11605,6 +12097,7 @@
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11623,7 +12116,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1710982393</v>
+        <v>1713755585</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -11633,10 +12126,11 @@
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11655,7 +12149,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1710990858</v>
+        <v>1713755622</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -11665,10 +12159,11 @@
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11687,7 +12182,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1710996357</v>
+        <v>1713834432</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -11697,10 +12192,11 @@
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11719,7 +12215,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1711004704</v>
+        <v>1713834498</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -11733,6 +12229,7 @@
         </is>
       </c>
       <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11751,7 +12248,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1711007406</v>
+        <v>1713834540</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -11761,10 +12258,11 @@
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11783,7 +12281,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1711008092</v>
+        <v>1713834568</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11793,10 +12291,15 @@
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11815,7 +12318,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1711057206</v>
+        <v>1713834599</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11825,10 +12328,11 @@
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11847,7 +12351,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1711064711</v>
+        <v>1713834643</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11861,6 +12365,7 @@
         </is>
       </c>
       <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11879,7 +12384,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1711067436</v>
+        <v>1713834669</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11893,6 +12398,7 @@
         </is>
       </c>
       <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11911,7 +12417,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1711067482</v>
+        <v>1713834692</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11925,6 +12431,7 @@
         </is>
       </c>
       <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11943,7 +12450,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1711068204</v>
+        <v>1713834719</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -11957,6 +12464,7 @@
         </is>
       </c>
       <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11975,7 +12483,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1711068238</v>
+        <v>1713834747</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -11989,6 +12497,7 @@
         </is>
       </c>
       <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12007,7 +12516,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1711068268</v>
+        <v>1713835180</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -12021,6 +12530,7 @@
         </is>
       </c>
       <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12039,7 +12549,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1711068325</v>
+        <v>1713842976</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -12053,6 +12563,7 @@
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12071,7 +12582,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1711070671</v>
+        <v>1713847738</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -12081,10 +12592,11 @@
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12103,7 +12615,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1711078242</v>
+        <v>1713848474</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -12113,10 +12625,11 @@
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12135,7 +12648,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1711081567</v>
+        <v>1713897567</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -12149,6 +12662,7 @@
         </is>
       </c>
       <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12167,7 +12681,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1711081591</v>
+        <v>1713911135</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -12177,10 +12691,11 @@
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12199,7 +12714,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1711154944</v>
+        <v>1713917260</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -12209,10 +12724,11 @@
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12231,7 +12747,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1711154965</v>
+        <v>1713918120</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -12245,6 +12761,7 @@
         </is>
       </c>
       <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12263,7 +12780,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1711154988</v>
+        <v>1713918153</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -12273,10 +12790,11 @@
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12295,7 +12813,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1711155011</v>
+        <v>1713918175</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -12305,10 +12823,11 @@
       <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12327,7 +12846,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1711155059</v>
+        <v>1713918757</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -12337,10 +12856,11 @@
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12359,7 +12879,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1711159133</v>
+        <v>1713918791</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -12369,10 +12889,11 @@
       <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12391,7 +12912,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1711162938</v>
+        <v>1713918821</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -12405,6 +12926,7 @@
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12423,7 +12945,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1711167600</v>
+        <v>1713918850</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -12433,10 +12955,15 @@
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12455,7 +12982,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1711167631</v>
+        <v>1713918915</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -12465,10 +12992,11 @@
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12487,7 +13015,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1711167658</v>
+        <v>1713923874</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -12497,10 +13025,15 @@
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12519,7 +13052,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1711168584</v>
+        <v>1713927989</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -12529,10 +13062,11 @@
       <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12551,7 +13085,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1711168607</v>
+        <v>1713931717</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -12565,6 +13099,7 @@
         </is>
       </c>
       <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12583,7 +13118,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1711168636</v>
+        <v>1713931761</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -12593,10 +13128,11 @@
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -12615,7 +13151,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1711168661</v>
+        <v>1713931789</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -12625,10 +13161,11 @@
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12647,7 +13184,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1711168741</v>
+        <v>1713932900</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -12657,10 +13194,11 @@
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12679,7 +13217,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1711170113</v>
+        <v>1713932917</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -12693,6 +13231,7 @@
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12711,7 +13250,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1711171644</v>
+        <v>1713932953</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -12721,10 +13260,11 @@
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12743,7 +13283,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1711172177</v>
+        <v>1713932985</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -12753,10 +13293,15 @@
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12775,7 +13320,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1711219460</v>
+        <v>1713933074</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -12785,10 +13330,11 @@
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -12807,7 +13353,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1711232818</v>
+        <v>1713933675</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -12821,6 +13367,7 @@
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12839,7 +13386,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1711238235</v>
+        <v>1713935953</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -12849,10 +13396,11 @@
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12871,7 +13419,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1711239565</v>
+        <v>1713936513</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -12881,10 +13429,11 @@
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -12903,7 +13452,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1711239604</v>
+        <v>1713993119</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -12917,6 +13466,7 @@
         </is>
       </c>
       <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -12935,7 +13485,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1711239633</v>
+        <v>1713999939</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12945,10 +13495,11 @@
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12967,7 +13518,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1711239859</v>
+        <v>1714002494</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12981,6 +13532,7 @@
         </is>
       </c>
       <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12999,7 +13551,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1711239892</v>
+        <v>1714002536</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -13009,10 +13561,11 @@
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13031,7 +13584,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1711239934</v>
+        <v>1714003538</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -13041,10 +13594,11 @@
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13063,7 +13617,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1711239961</v>
+        <v>1714003563</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -13073,10 +13627,11 @@
       <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13095,7 +13650,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1711240076</v>
+        <v>1714003607</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -13109,6 +13664,7 @@
         </is>
       </c>
       <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13127,7 +13683,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1711240940</v>
+        <v>1714010610</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -13141,6 +13697,7 @@
         </is>
       </c>
       <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13159,7 +13716,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1711240981</v>
+        <v>1714014502</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -13173,6 +13730,7 @@
         </is>
       </c>
       <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -13191,7 +13749,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1711241008</v>
+        <v>1714014535</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -13205,6 +13763,7 @@
         </is>
       </c>
       <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13223,7 +13782,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1711241967</v>
+        <v>1714080396</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -13237,6 +13796,7 @@
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -13255,7 +13815,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1711241990</v>
+        <v>1714087412</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -13269,6 +13829,7 @@
         </is>
       </c>
       <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13287,7 +13848,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1711242019</v>
+        <v>1714091628</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -13301,6 +13862,7 @@
         </is>
       </c>
       <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13319,7 +13881,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1711242041</v>
+        <v>1714097985</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -13329,10 +13891,11 @@
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13351,7 +13914,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1711242148</v>
+        <v>1714101787</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -13361,10 +13924,11 @@
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13383,7 +13947,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1711245160</v>
+        <v>1714101807</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -13393,10 +13957,11 @@
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -13415,7 +13980,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1711249484</v>
+        <v>1714157275</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -13425,10 +13990,11 @@
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -13447,7 +14013,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1711251635</v>
+        <v>1714170180</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -13461,6 +14027,7 @@
         </is>
       </c>
       <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -13479,7 +14046,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1711251675</v>
+        <v>1714177286</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -13489,10 +14056,11 @@
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13511,7 +14079,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1711251700</v>
+        <v>1714184871</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -13521,10 +14089,15 @@
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -13543,7 +14116,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1711254940</v>
+        <v>1714188648</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -13553,10 +14126,11 @@
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -13575,7 +14149,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1711254964</v>
+        <v>1714196814</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -13589,6 +14163,7 @@
         </is>
       </c>
       <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -13607,7 +14182,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1711254993</v>
+        <v>1714198628</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -13617,10 +14192,11 @@
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -13639,7 +14215,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1711255021</v>
+        <v>1714199313</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -13649,10 +14225,11 @@
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -13671,7 +14248,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1711255100</v>
+        <v>1714242908</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -13681,10 +14258,11 @@
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -13703,7 +14281,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1711256107</v>
+        <v>1714256469</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -13717,6 +14295,7 @@
         </is>
       </c>
       <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -13735,7 +14314,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1711257994</v>
+        <v>1714263413</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -13745,10 +14324,11 @@
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -13767,7 +14347,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1711258676</v>
+        <v>1714271627</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -13777,10 +14357,15 @@
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13799,7 +14384,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1711306944</v>
+        <v>1714275776</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -13809,10 +14394,11 @@
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -13831,7 +14417,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1711319561</v>
+        <v>1714283396</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -13845,6 +14431,7 @@
         </is>
       </c>
       <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -13863,7 +14450,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1711325219</v>
+        <v>1714285133</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -13873,10 +14460,11 @@
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -13895,7 +14483,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1711331520</v>
+        <v>1714285799</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -13905,906 +14493,11 @@
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>1711335495</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>1711338592</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>1711338620</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>1711338649</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>1711340776</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>1711340791</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>1711340818</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>1711340847</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>1711340898</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>1711341227</v>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>1711342952</v>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>1711343597</v>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H433" t="inlineStr"/>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>1711391826</v>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr"/>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>1711405602</v>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr"/>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>1711412132</v>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>1711414636</v>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr"/>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D438" t="n">
-        <v>1711414671</v>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D439" t="n">
-        <v>1711414693</v>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr"/>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D440" t="n">
-        <v>1711415891</v>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D441" t="n">
-        <v>1711415922</v>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D442" t="n">
-        <v>1711415951</v>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr"/>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D443" t="n">
-        <v>1711415974</v>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr"/>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D444" t="n">
-        <v>1711416052</v>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr"/>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D445" t="n">
-        <v>1711418826</v>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr"/>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D446" t="n">
-        <v>1711422489</v>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr"/>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D447" t="n">
-        <v>1711426647</v>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D448" t="n">
-        <v>1711426676</v>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D449" t="n">
-        <v>1711426697</v>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
